--- a/data/trans_bre/IP04F-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Habitat-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 4,08</t>
+          <t>-6,4; 4,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 7,14</t>
+          <t>-2,7; 7,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-61,95; 82,98</t>
+          <t>-62,39; 87,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 208,15</t>
+          <t>-36,04; 196,89</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 5,86</t>
+          <t>-2,07; 6,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 2,67</t>
+          <t>-5,37; 2,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,56; 97,3</t>
+          <t>-22,78; 105,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,53; 44,12</t>
+          <t>-51,64; 45,36</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 4,43</t>
+          <t>-6,99; 4,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 2,84</t>
+          <t>-7,06; 2,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-47,61; 55,3</t>
+          <t>-49,79; 50,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-60,38; 49,25</t>
+          <t>-60,59; 53,08</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 9,56</t>
+          <t>-1,08; 9,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 10,04</t>
+          <t>-0,17; 10,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 129,73</t>
+          <t>-11,84; 145,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 170,98</t>
+          <t>-2,5; 160,87</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,97</t>
+          <t>-1,18; 3,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,64</t>
+          <t>-1,23; 3,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 52,9</t>
+          <t>-11,65; 49,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 54,23</t>
+          <t>-15,12; 51,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04F-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Habitat-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 4,02</t>
+          <t>-6,14; 4,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,31</t>
+          <t>-2,63; 7,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-62,39; 87,14</t>
+          <t>-63,02; 84,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 196,89</t>
+          <t>-37,67; 202,75</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 6,41</t>
+          <t>-2,31; 6,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,65</t>
+          <t>-5,26; 2,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 105,37</t>
+          <t>-24,7; 104,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,64; 45,36</t>
+          <t>-50,87; 44,49</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 4,01</t>
+          <t>-6,34; 4,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,86</t>
+          <t>-6,92; 3,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 50,11</t>
+          <t>-47,03; 60,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-60,59; 53,08</t>
+          <t>-61,48; 55,96</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 9,89</t>
+          <t>-0,81; 10,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 10,0</t>
+          <t>-0,05; 10,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 145,7</t>
+          <t>-7,65; 157,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 160,87</t>
+          <t>-3,16; 182,51</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,94</t>
+          <t>-1,0; 4,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,48</t>
+          <t>-1,13; 3,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 49,63</t>
+          <t>-9,96; 52,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 51,07</t>
+          <t>-13,71; 50,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04F-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Habitat-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 4,14</t>
+          <t>-6,2; 4,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,14</t>
+          <t>-2,45; 7,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-63,02; 84,89</t>
+          <t>-61,95; 82,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 202,75</t>
+          <t>-33,64; 208,15</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 6,22</t>
+          <t>-2,58; 5,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 2,84</t>
+          <t>-5,49; 2,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 104,81</t>
+          <t>-25,56; 97,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,87; 44,49</t>
+          <t>-52,53; 44,12</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 4,84</t>
+          <t>-6,54; 4,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 3,31</t>
+          <t>-6,82; 2,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-47,03; 60,2</t>
+          <t>-47,61; 55,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 55,96</t>
+          <t>-60,38; 49,25</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 10,55</t>
+          <t>-0,92; 9,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 10,39</t>
+          <t>-0,08; 10,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 157,81</t>
+          <t>-11,64; 129,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 182,51</t>
+          <t>-1,04; 170,98</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,02</t>
+          <t>-1,08; 3,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,37</t>
+          <t>-1,27; 3,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 52,58</t>
+          <t>-10,63; 52,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 50,74</t>
+          <t>-14,68; 54,23</t>
         </is>
       </c>
     </row>
